--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/KENTUCKY_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/KENTUCKY_2019.xlsx
@@ -4056,7 +4056,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C206">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C502">
